--- a/VanHanhCD1/wwwroot/templates/BMVH_QHCVeVien.xlsx
+++ b/VanHanhCD1/wwwroot/templates/BMVH_QHCVeVien.xlsx
@@ -5,21 +5,30 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\03. Project Hoa Phat\07. Backend\VanHanhCD1_API-main\VanHanhCD1\wwwroot\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02. Du An Hoa Phat\API\VanHanhCD1_API-release\VanHanhCD1\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFEEB13-2253-4B1B-B1B1-0986E50B110B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E469F8F-619C-4CD3-8343-6E7A61B07E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="5" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -583,7 +592,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -646,6 +655,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -658,35 +685,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -698,9 +710,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -720,9 +729,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1455,70 +1461,70 @@
       <c r="A1" s="5"/>
       <c r="B1" s="5"/>
       <c r="C1" s="11"/>
-      <c r="D1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="29" t="s">
+      <c r="D1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
     </row>
     <row r="2" spans="1:22" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="11"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="22" t="s">
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
     </row>
     <row r="3" spans="1:22" s="7" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="11"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
       <c r="R3" s="4"/>
       <c r="S3" s="6"/>
       <c r="T3" s="6"/>
@@ -1532,109 +1538,109 @@
       <c r="B5" s="8"/>
       <c r="C5" s="13"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="32"/>
-      <c r="P5" s="32"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
+      <c r="P5" s="34"/>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
       <c r="S5" s="8"/>
       <c r="T5" s="8"/>
     </row>
     <row r="6" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="30" t="s">
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="30"/>
-      <c r="R6" s="30"/>
-      <c r="S6" s="30"/>
-      <c r="T6" s="30"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="22"/>
+      <c r="S6" s="22"/>
+      <c r="T6" s="22"/>
     </row>
     <row r="7" spans="1:22" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="34"/>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30" t="s">
+      <c r="A7" s="24"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30" t="s">
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30" t="s">
+      <c r="L7" s="22"/>
+      <c r="M7" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N7" s="30"/>
+      <c r="N7" s="22"/>
       <c r="O7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q7" s="30" t="s">
+      <c r="Q7" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="R7" s="30"/>
-      <c r="S7" s="30" t="s">
+      <c r="R7" s="22"/>
+      <c r="S7" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="T7" s="30"/>
+      <c r="T7" s="22"/>
     </row>
     <row r="8" spans="1:22" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="30"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="22"/>
       <c r="H8" s="2">
         <v>1</v>
       </c>
@@ -1676,7 +1682,7 @@
       </c>
     </row>
     <row r="9" spans="1:22" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="25" t="s">
         <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1756,7 +1762,7 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="33"/>
+      <c r="A10" s="25"/>
       <c r="B10" s="2" t="s">
         <v>24</v>
       </c>
@@ -1834,7 +1840,7 @@
       </c>
     </row>
     <row r="11" spans="1:22" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="33"/>
+      <c r="A11" s="25"/>
       <c r="B11" s="2" t="s">
         <v>25</v>
       </c>
@@ -1912,7 +1918,7 @@
       </c>
     </row>
     <row r="12" spans="1:22" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="33"/>
+      <c r="A12" s="25"/>
       <c r="B12" s="2" t="s">
         <v>26</v>
       </c>
@@ -1990,7 +1996,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="33"/>
+      <c r="A13" s="25"/>
       <c r="B13" s="2" t="s">
         <v>27</v>
       </c>
@@ -2068,7 +2074,7 @@
       </c>
     </row>
     <row r="14" spans="1:22" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="33"/>
+      <c r="A14" s="25"/>
       <c r="B14" s="2" t="s">
         <v>28</v>
       </c>
@@ -2146,7 +2152,7 @@
       </c>
     </row>
     <row r="15" spans="1:22" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="33"/>
+      <c r="A15" s="25"/>
       <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
@@ -2224,7 +2230,7 @@
       </c>
     </row>
     <row r="16" spans="1:22" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="33"/>
+      <c r="A16" s="25"/>
       <c r="B16" s="2" t="s">
         <v>30</v>
       </c>
@@ -2302,7 +2308,7 @@
       </c>
     </row>
     <row r="17" spans="1:20" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="33"/>
+      <c r="A17" s="25"/>
       <c r="B17" s="2" t="s">
         <v>31</v>
       </c>
@@ -2380,7 +2386,7 @@
       </c>
     </row>
     <row r="18" spans="1:20" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="33"/>
+      <c r="A18" s="25"/>
       <c r="B18" s="2" t="s">
         <v>32</v>
       </c>
@@ -2458,7 +2464,7 @@
       </c>
     </row>
     <row r="19" spans="1:20" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="33"/>
+      <c r="A19" s="25"/>
       <c r="B19" s="2" t="s">
         <v>33</v>
       </c>
@@ -2536,7 +2542,7 @@
       </c>
     </row>
     <row r="20" spans="1:20" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="33"/>
+      <c r="A20" s="25"/>
       <c r="B20" s="2" t="s">
         <v>34</v>
       </c>
@@ -2614,7 +2620,7 @@
       </c>
     </row>
     <row r="21" spans="1:20" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="33" t="s">
+      <c r="A21" s="25" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -2694,7 +2700,7 @@
       </c>
     </row>
     <row r="22" spans="1:20" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="33"/>
+      <c r="A22" s="25"/>
       <c r="B22" s="2" t="s">
         <v>36</v>
       </c>
@@ -2772,7 +2778,7 @@
       </c>
     </row>
     <row r="23" spans="1:20" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="33"/>
+      <c r="A23" s="25"/>
       <c r="B23" s="2" t="s">
         <v>37</v>
       </c>
@@ -2850,7 +2856,7 @@
       </c>
     </row>
     <row r="24" spans="1:20" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="33"/>
+      <c r="A24" s="25"/>
       <c r="B24" s="2" t="s">
         <v>38</v>
       </c>
@@ -2928,7 +2934,7 @@
       </c>
     </row>
     <row r="25" spans="1:20" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="33"/>
+      <c r="A25" s="25"/>
       <c r="B25" s="2" t="s">
         <v>39</v>
       </c>
@@ -3006,7 +3012,7 @@
       </c>
     </row>
     <row r="26" spans="1:20" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="33"/>
+      <c r="A26" s="25"/>
       <c r="B26" s="2" t="s">
         <v>40</v>
       </c>
@@ -3084,7 +3090,7 @@
       </c>
     </row>
     <row r="27" spans="1:20" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="33"/>
+      <c r="A27" s="25"/>
       <c r="B27" s="2" t="s">
         <v>41</v>
       </c>
@@ -3162,7 +3168,7 @@
       </c>
     </row>
     <row r="28" spans="1:20" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33"/>
+      <c r="A28" s="25"/>
       <c r="B28" s="2" t="s">
         <v>42</v>
       </c>
@@ -3240,7 +3246,7 @@
       </c>
     </row>
     <row r="29" spans="1:20" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="33"/>
+      <c r="A29" s="25"/>
       <c r="B29" s="2" t="s">
         <v>43</v>
       </c>
@@ -3318,7 +3324,7 @@
       </c>
     </row>
     <row r="30" spans="1:20" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="33"/>
+      <c r="A30" s="25"/>
       <c r="B30" s="2" t="s">
         <v>44</v>
       </c>
@@ -3396,7 +3402,7 @@
       </c>
     </row>
     <row r="31" spans="1:20" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="33"/>
+      <c r="A31" s="25"/>
       <c r="B31" s="2" t="s">
         <v>45</v>
       </c>
@@ -3474,7 +3480,7 @@
       </c>
     </row>
     <row r="32" spans="1:20" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="33"/>
+      <c r="A32" s="25"/>
       <c r="B32" s="2" t="s">
         <v>46</v>
       </c>
@@ -3552,127 +3558,154 @@
       </c>
     </row>
     <row r="33" spans="1:21" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="35" t="s">
+      <c r="A33" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="35"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="35"/>
-      <c r="J33" s="35"/>
-      <c r="K33" s="35"/>
-      <c r="L33" s="35"/>
-      <c r="M33" s="35"/>
-      <c r="N33" s="35"/>
-      <c r="O33" s="35"/>
-      <c r="P33" s="35"/>
-      <c r="Q33" s="35"/>
-      <c r="R33" s="35"/>
-      <c r="S33" s="35"/>
-      <c r="T33" s="35"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="26"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="26"/>
+      <c r="O33" s="26"/>
+      <c r="P33" s="26"/>
+      <c r="Q33" s="26"/>
+      <c r="R33" s="26"/>
+      <c r="S33" s="26"/>
+      <c r="T33" s="26"/>
     </row>
     <row r="34" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="27" t="s">
+      <c r="A34" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B34" s="26" t="s">
+      <c r="B34" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26" t="s">
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="27" t="s">
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="23"/>
+      <c r="K34" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="L34" s="26" t="s">
+      <c r="L34" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="M34" s="26"/>
-      <c r="N34" s="26"/>
-      <c r="O34" s="26"/>
-      <c r="P34" s="26" t="s">
+      <c r="M34" s="23"/>
+      <c r="N34" s="23"/>
+      <c r="O34" s="23"/>
+      <c r="P34" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="Q34" s="26"/>
-      <c r="R34" s="26"/>
-      <c r="S34" s="26"/>
-      <c r="T34" s="26"/>
+      <c r="Q34" s="23"/>
+      <c r="R34" s="23"/>
+      <c r="S34" s="23"/>
+      <c r="T34" s="23"/>
     </row>
     <row r="35" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="27"/>
-      <c r="B35" s="26" t="s">
+      <c r="A35" s="25"/>
+      <c r="B35" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="26"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="26" t="s">
+      <c r="C35" s="23"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="G35" s="26"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="27"/>
-      <c r="L35" s="26" t="s">
+      <c r="G35" s="23"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="27"/>
+      <c r="J35" s="27"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="M35" s="26"/>
-      <c r="N35" s="26"/>
-      <c r="O35" s="26"/>
-      <c r="P35" s="26" t="s">
+      <c r="M35" s="23"/>
+      <c r="N35" s="23"/>
+      <c r="O35" s="23"/>
+      <c r="P35" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="Q35" s="26"/>
-      <c r="R35" s="26"/>
-      <c r="S35" s="26"/>
-      <c r="T35" s="26"/>
+      <c r="Q35" s="23"/>
+      <c r="R35" s="23"/>
+      <c r="S35" s="23"/>
+      <c r="T35" s="23"/>
       <c r="U35" s="9"/>
     </row>
     <row r="36" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="27"/>
-      <c r="B36" s="26" t="s">
+      <c r="A36" s="25"/>
+      <c r="B36" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="C36" s="26"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="26" t="s">
+      <c r="C36" s="23"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="G36" s="26"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="31"/>
-      <c r="J36" s="31"/>
-      <c r="K36" s="27"/>
-      <c r="L36" s="26" t="s">
+      <c r="G36" s="23"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="27"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="M36" s="26"/>
-      <c r="N36" s="26"/>
-      <c r="O36" s="26"/>
-      <c r="P36" s="26" t="s">
+      <c r="M36" s="23"/>
+      <c r="N36" s="23"/>
+      <c r="O36" s="23"/>
+      <c r="P36" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="Q36" s="26"/>
-      <c r="R36" s="26"/>
-      <c r="S36" s="26"/>
-      <c r="T36" s="26"/>
+      <c r="Q36" s="23"/>
+      <c r="R36" s="23"/>
+      <c r="S36" s="23"/>
+      <c r="T36" s="23"/>
       <c r="U36" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="K34:K36"/>
+    <mergeCell ref="D1:Q3"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O6:T6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="E5:P5"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="R35:T35"/>
+    <mergeCell ref="R36:T36"/>
+    <mergeCell ref="P34:T34"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="F34:J34"/>
+    <mergeCell ref="H35:J35"/>
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="Q7:R7"/>
     <mergeCell ref="P35:Q35"/>
@@ -3689,33 +3722,6 @@
     <mergeCell ref="L35:M35"/>
     <mergeCell ref="L36:M36"/>
     <mergeCell ref="A33:T33"/>
-    <mergeCell ref="R35:T35"/>
-    <mergeCell ref="R36:T36"/>
-    <mergeCell ref="P34:T34"/>
-    <mergeCell ref="N36:O36"/>
-    <mergeCell ref="F34:J34"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="K34:K36"/>
-    <mergeCell ref="D1:Q3"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="G6:G8"/>
-    <mergeCell ref="H6:N6"/>
-    <mergeCell ref="O6:T6"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="E5:P5"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="M7:N7"/>
   </mergeCells>
   <pageMargins left="0.76041666666666663" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId1"/>
@@ -3737,70 +3743,70 @@
       <c r="A1" s="5"/>
       <c r="B1" s="5"/>
       <c r="C1" s="11"/>
-      <c r="D1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="29" t="s">
+      <c r="D1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
     </row>
     <row r="2" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="11"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="22" t="s">
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
     </row>
     <row r="3" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="11"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
       <c r="R3" s="4"/>
       <c r="S3" s="6"/>
       <c r="T3" s="6"/>
@@ -3813,31 +3819,31 @@
       <c r="B5" s="8"/>
       <c r="C5" s="13"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="32"/>
-      <c r="P5" s="32"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
+      <c r="P5" s="34"/>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
       <c r="S5" s="8"/>
       <c r="T5" s="8"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
       <c r="D6" s="16" t="s">
         <v>56</v>
       </c>
@@ -3915,11 +3921,11 @@
       </c>
     </row>
     <row r="7" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
       <c r="D7" s="18" t="s">
         <v>77</v>
       </c>
@@ -3949,11 +3955,11 @@
       <c r="AB7" s="21"/>
     </row>
     <row r="8" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
       <c r="D8" s="18" t="s">
         <v>57</v>
       </c>
@@ -3983,11 +3989,11 @@
       <c r="AB8" s="21"/>
     </row>
     <row r="9" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
       <c r="D9" s="18" t="s">
         <v>58</v>
       </c>
@@ -4017,11 +4023,11 @@
       <c r="AB9" s="21"/>
     </row>
     <row r="10" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
       <c r="D10" s="18" t="s">
         <v>59</v>
       </c>
@@ -4088,7 +4094,7 @@
       <c r="A12" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="36" t="s">
+      <c r="B12" s="37" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="19">
@@ -4124,7 +4130,7 @@
     </row>
     <row r="13" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="44"/>
-      <c r="B13" s="37"/>
+      <c r="B13" s="38"/>
       <c r="C13" s="19">
         <v>2</v>
       </c>
@@ -4158,7 +4164,7 @@
     </row>
     <row r="14" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="44"/>
-      <c r="B14" s="38"/>
+      <c r="B14" s="39"/>
       <c r="C14" s="19">
         <v>3</v>
       </c>
@@ -4331,7 +4337,7 @@
       <c r="AB18" s="21"/>
     </row>
     <row r="19" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="37" t="s">
         <v>69</v>
       </c>
       <c r="B19" s="20" t="s">
@@ -4369,7 +4375,7 @@
       <c r="AB19" s="21"/>
     </row>
     <row r="20" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="37"/>
+      <c r="A20" s="38"/>
       <c r="B20" s="20" t="s">
         <v>17</v>
       </c>
@@ -4405,8 +4411,8 @@
       <c r="AB20" s="21"/>
     </row>
     <row r="21" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="37"/>
-      <c r="B21" s="36" t="s">
+      <c r="A21" s="38"/>
+      <c r="B21" s="37" t="s">
         <v>72</v>
       </c>
       <c r="C21" s="19" t="s">
@@ -4441,8 +4447,8 @@
       <c r="AB21" s="21"/>
     </row>
     <row r="22" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="37"/>
-      <c r="B22" s="38"/>
+      <c r="A22" s="38"/>
+      <c r="B22" s="39"/>
       <c r="C22" s="19" t="s">
         <v>21</v>
       </c>
@@ -4475,8 +4481,8 @@
       <c r="AB22" s="21"/>
     </row>
     <row r="23" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="37"/>
-      <c r="B23" s="36" t="s">
+      <c r="A23" s="38"/>
+      <c r="B23" s="37" t="s">
         <v>19</v>
       </c>
       <c r="C23" s="19" t="s">
@@ -4511,8 +4517,8 @@
       <c r="AB23" s="21"/>
     </row>
     <row r="24" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="38"/>
-      <c r="B24" s="38"/>
+      <c r="A24" s="39"/>
+      <c r="B24" s="39"/>
       <c r="C24" s="19" t="s">
         <v>21</v>
       </c>
@@ -4546,12 +4552,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D1:Q3"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="E5:P5"/>
-    <mergeCell ref="A6:C6"/>
     <mergeCell ref="A19:A24"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="B23:B24"/>
@@ -4563,6 +4563,12 @@
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="B17:B18"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D1:Q3"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="E5:P5"/>
+    <mergeCell ref="A6:C6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
